--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,20 +854,14 @@
           <t>038/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4500010750</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1000024200</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4500010750</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1000024200</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -951,6 +945,212 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/II/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4500010748</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1000024201</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>29459820</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3240580.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>32700400.2</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:02:27</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>29459820</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/II/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1000024205</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>24499020</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2694892.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27193912.2</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:04:02</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>24499020</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,20 +1054,14 @@
           <t>035/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4500010749</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1000024205</t>
-        </is>
+      <c r="B7" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4500010749</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1000024205</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1151,6 +1145,212 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>126/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4500011203</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1000025162</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>6919250</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>761117.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7680367.5</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:13:55</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>6919250</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>127/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4500011236</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1000025165</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/WS/IV/2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>890007885</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>773919900</v>
+      </c>
+      <c r="P9" t="n">
+        <v>116087985</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>97900867.34999999</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>987908752.35</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:17:02</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>890007885</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0</v>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Database_Billing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database_Billing'!$A$1:$Z$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,45 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A7F3D0"/>
+        <bgColor rgb="00A7F3D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +73,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,948 +467,1077 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nomor Invoice Resmi</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Kontrak No.</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nomor PO</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Nomor SA / WAN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>PI No.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Alamat Customer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>NPWP Customer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tanggal Invoice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jatuh Tempo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Keterangan Invoice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Informasi Bank</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Nilai Invoice</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Gunakan Professional Sum</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Add Cost</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Management Fee</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PPN Nominal</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PPh Nominal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Netto</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Kena PPN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Kena PPh</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Tarif PPh</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Update Terakhir</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Nilai Gross (Bruto)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Diskon Nominal (10%)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Gunakan Estimasi Sum</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>468/BSS-JOB/XII/2025</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>7203250036</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>4500010394</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>1000023594</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>001/BSS-JOB/WH/X/2025</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="2" t="n">
         <v>61047000</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>6715170</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>67762170</v>
       </c>
-      <c r="T2" t="b">
+      <c r="T2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="U2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>2026-09-14 20:08:25</t>
         </is>
       </c>
-      <c r="X2" t="n">
+      <c r="X2" s="2" t="n">
         <v>61047000</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="Y2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>036/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>7207250142</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>4500010745</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1000024198</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>51177360</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3" t="n">
         <v>5629509.6</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>56806869.6</v>
       </c>
-      <c r="T3" t="b">
+      <c r="T3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="U3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>2026-09-14 20:33:58</t>
         </is>
       </c>
-      <c r="X3" t="n">
+      <c r="X3" s="3" t="n">
         <v>51177360</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="Y3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>037/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>7207250142</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>4500010746</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>1000024199</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="2" t="n">
         <v>73803990</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
         <v>8118438.9</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>81922428.90000001</v>
       </c>
-      <c r="T4" t="b">
+      <c r="T4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="U4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>2026-09-14 20:39:06</t>
         </is>
       </c>
-      <c r="X4" t="n">
+      <c r="X4" s="2" t="n">
         <v>73803990</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="Y4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>038/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>7207250142</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>4500010750</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>1000024200</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>30507750</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>3355852.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>33863602.5</v>
       </c>
-      <c r="T5" t="b">
+      <c r="T5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="U5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>2026-09-14 20:41:24</t>
         </is>
       </c>
-      <c r="X5" t="n">
+      <c r="X5" s="3" t="n">
         <v>30507750</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>039/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>7207250142</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>4500010748</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>1000024201</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="2" t="n">
         <v>29459820</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>3240580.2</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>32700400.2</v>
       </c>
-      <c r="T6" t="b">
+      <c r="T6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="U6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>2026-09-15 03:02:27</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="X6" s="2" t="n">
         <v>29459820</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="Y6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>035/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>7207250142</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>4500010749</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>1000024205</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>24499020</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>2694892.2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>27193912.2</v>
       </c>
-      <c r="T7" t="b">
+      <c r="T7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="U7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t>2026-09-15 03:04:02</t>
         </is>
       </c>
-      <c r="X7" t="n">
+      <c r="X7" s="3" t="n">
         <v>24499020</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>126/BSS-JOB/VI/2026</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>7201250141</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>4500011203</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="2" t="n">
         <v>1000025162</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="2" t="n">
         <v>6919250</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
         <v>761117.5</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>7680367.5</v>
       </c>
-      <c r="T8" t="b">
+      <c r="T8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="U8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>2026-09-15 08:13:55</t>
         </is>
       </c>
-      <c r="X8" t="n">
+      <c r="X8" s="2" t="n">
         <v>6919250</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="Y8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>127/BSS-JOB/VI/2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4500011236</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1000025165</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/WS/IV/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>890007885</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>773919900</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>116087985</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>97900867.34999999</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>987908752.35</v>
+      </c>
+      <c r="T9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:17:02</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>890007885</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026test</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4500011236</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1000025165</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>45000000test</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100012345test</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>002.796.802.3-081.000</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>890007885</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="M10" s="2" t="n">
+        <v>13013460</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>1431480.6</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>14444940.6</v>
+      </c>
+      <c r="T10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>773919900</v>
-      </c>
-      <c r="P9" t="n">
-        <v>116087985</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>97900867.34999999</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>987908752.35</v>
-      </c>
-      <c r="T9" t="b">
+      <c r="U10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:33:48</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>14459400</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>1445940</v>
+      </c>
+      <c r="Z10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2026-09-15 08:17:02</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
-        <v>890007885</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Database_Billing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database_Billing'!$A$1:$Z$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database_Billing'!$A$1:$AA$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,7 @@
     <col width="25" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -629,6 +630,11 @@
           <t>Gunakan Estimasi Sum</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>At Cost</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -729,6 +735,7 @@
       <c r="Z2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -829,6 +836,7 @@
       <c r="Z3" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -929,6 +937,7 @@
       <c r="Z4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1029,6 +1038,7 @@
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1129,6 +1139,7 @@
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1229,6 +1240,7 @@
       <c r="Z7" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1329,6 +1341,7 @@
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1337,13 +1350,15 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>4500011236</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>1000025165</v>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1000024507</t>
+        </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -1386,25 +1401,23 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>890007885</v>
+        <v>116087985</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="3" t="n">
-        <v>773919900</v>
-      </c>
+      <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="n">
         <v>116087985</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>97900867.34999999</v>
+        <v>12769678</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>987908752.35</v>
+        <v>128857663</v>
       </c>
       <c r="T9" s="3" t="b">
         <v>1</v>
@@ -1417,16 +1430,19 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 08:17:02</t>
+          <t>2026-09-21 15:17:48</t>
         </is>
       </c>
       <c r="X9" s="3" t="n">
-        <v>890007885</v>
+        <v>116087985</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1436,10 +1452,8 @@
           <t>028/BSS-JOB/WS/VIII/2026test</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B10" s="2" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1535,9 +1549,10 @@
       <c r="Z10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AA10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z10"/>
+  <autoFilter ref="A1:AA10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Database_Billing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database_Billing'!$A$1:$AA$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database_Billing'!$A$1:$AA$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,10 +467,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -1350,14 +1350,14 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>4500011236</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1000024507</t>
+          <t>1000025165</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>116087985</v>
+        <v>890007885</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
@@ -1411,13 +1411,13 @@
         <v>116087985</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>12769678</v>
+        <v>97900867</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>128857663</v>
+        <v>987908752</v>
       </c>
       <c r="T9" s="3" t="b">
         <v>1</v>
@@ -1430,11 +1430,11 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 15:17:48</t>
+          <t>2026-09-21 17:15:04</t>
         </is>
       </c>
       <c r="X9" s="3" t="n">
-        <v>116087985</v>
+        <v>890007885</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>0</v>
@@ -1443,116 +1443,11 @@
         <v>0</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>028/BSS-JOB/WS/VIII/2026test</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>45000000test</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>100012345test</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>002.796.802.3-081.000</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>13013460</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>1431480.6</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>14444940.6</v>
-      </c>
-      <c r="T10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15 10:33:48</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>14459400</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>1445940</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
+        <v>773919900</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA10"/>
+  <autoFilter ref="A1:AA9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>